--- a/tests/fixtures/ratio_z1_2026-04-10.xlsx
+++ b/tests/fixtures/ratio_z1_2026-04-10.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="final_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="merged_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/tests/fixtures/ratio_z1_2026-04-10.xlsx
+++ b/tests/fixtures/ratio_z1_2026-04-10.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="merged_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="invalid_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="valid_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="calc_data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +416,582 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pertype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1204,4 +1783,803 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pertype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>concept_ratio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value_num</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>value_den</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>value_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>175</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.714285714285714</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>175</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>40</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>275</v>
+      </c>
+      <c r="H12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>275</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.999999999999999e-11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.999999999999999e-11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>160</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>